--- a/datasets/test/イチゴ/59期収量（実験棟）.xlsx
+++ b/datasets/test/イチゴ/59期収量（実験棟）.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\B000005_営業本部　ハウス備品事業本部\障がい者農園事業部\004_はーとふる農園　愛川\農業指導員\砂栽培研究\イチゴ栽培\59期\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58579527-67E5-4ADD-85DF-AE6381F8712B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D3B489-87DC-4A18-AFB6-9E76DB45DB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="18">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -137,6 +137,36 @@
   </si>
   <si>
     <t>やよいひめ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収量計</t>
+    <rPh sb="0" eb="2">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ取り入れ済み</t>
+    <rPh sb="3" eb="4">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>破棄</t>
+    <rPh sb="0" eb="2">
+      <t>ハキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -463,14 +493,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:K120"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.08203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,8 +522,14 @@
       <c r="G1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>46015</v>
       </c>
@@ -509,8 +545,12 @@
       <c r="F2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="I2">
+        <f>D2+E2</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>46015</v>
       </c>
@@ -526,8 +566,12 @@
       <c r="F3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="I3">
+        <f t="shared" ref="I3:I66" si="0">D3+E3</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>46015</v>
       </c>
@@ -543,8 +587,12 @@
       <c r="F4">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>46029</v>
       </c>
@@ -560,8 +608,12 @@
       <c r="F5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>46029</v>
       </c>
@@ -583,8 +635,12 @@
       <c r="G6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>46029</v>
       </c>
@@ -606,8 +662,12 @@
       <c r="G7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>46029</v>
       </c>
@@ -629,8 +689,12 @@
       <c r="G8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>46029</v>
       </c>
@@ -652,8 +716,12 @@
       <c r="G9">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>46036</v>
       </c>
@@ -666,8 +734,12 @@
       <c r="D10">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>46036</v>
       </c>
@@ -683,8 +755,12 @@
       <c r="E11">
         <v>23</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>46036</v>
       </c>
@@ -697,8 +773,12 @@
       <c r="D12">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>46036</v>
       </c>
@@ -714,8 +794,12 @@
       <c r="E13">
         <v>91</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>46036</v>
       </c>
@@ -731,8 +815,12 @@
       <c r="E14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>46042</v>
       </c>
@@ -745,8 +833,12 @@
       <c r="D15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>46042</v>
       </c>
@@ -759,8 +851,12 @@
       <c r="D16">
         <v>179</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>46042</v>
       </c>
@@ -773,8 +869,12 @@
       <c r="D17">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>46042</v>
       </c>
@@ -787,8 +887,12 @@
       <c r="D18">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>46042</v>
       </c>
@@ -801,8 +905,12 @@
       <c r="D19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>46042</v>
       </c>
@@ -818,8 +926,12 @@
       <c r="E20">
         <v>127</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>46044</v>
       </c>
@@ -832,8 +944,12 @@
       <c r="D21">
         <v>38</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>46044</v>
       </c>
@@ -846,8 +962,12 @@
       <c r="D22">
         <v>185</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>46044</v>
       </c>
@@ -860,8 +980,12 @@
       <c r="D23">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>46044</v>
       </c>
@@ -877,8 +1001,12 @@
       <c r="E24">
         <v>45</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>46048</v>
       </c>
@@ -891,8 +1019,12 @@
       <c r="D25">
         <v>89</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="I25">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>46048</v>
       </c>
@@ -908,8 +1040,12 @@
       <c r="E26">
         <v>57</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>46048</v>
       </c>
@@ -922,8 +1058,12 @@
       <c r="D27">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="I27">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>46048</v>
       </c>
@@ -936,8 +1076,12 @@
       <c r="D28">
         <v>65</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="I28">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>46048</v>
       </c>
@@ -950,8 +1094,12 @@
       <c r="D29">
         <v>63</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="I29">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>46048</v>
       </c>
@@ -964,8 +1112,12 @@
       <c r="D30">
         <v>12</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="I30">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>46048</v>
       </c>
@@ -981,8 +1133,12 @@
       <c r="E31">
         <v>148</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="I31">
+        <f t="shared" si="0"/>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>46050</v>
       </c>
@@ -995,8 +1151,12 @@
       <c r="D32">
         <v>40</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="I32">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>46050</v>
       </c>
@@ -1009,8 +1169,12 @@
       <c r="D33">
         <v>262</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="I33">
+        <f t="shared" si="0"/>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>46050</v>
       </c>
@@ -1026,8 +1190,12 @@
       <c r="E34">
         <v>8</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="I34">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>46050</v>
       </c>
@@ -1040,8 +1208,12 @@
       <c r="D35">
         <v>47</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="I35">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>46050</v>
       </c>
@@ -1057,8 +1229,12 @@
       <c r="E36">
         <v>23</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="I36">
+        <f t="shared" si="0"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>46050</v>
       </c>
@@ -1071,8 +1247,12 @@
       <c r="E37">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="I37">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>46055</v>
       </c>
@@ -1088,8 +1268,12 @@
       <c r="E38">
         <v>14</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="I38">
+        <f t="shared" si="0"/>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="1">
         <v>46055</v>
       </c>
@@ -1102,8 +1286,12 @@
       <c r="D39">
         <v>652</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="I39">
+        <f t="shared" si="0"/>
+        <v>652</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>46055</v>
       </c>
@@ -1116,8 +1304,12 @@
       <c r="D40">
         <v>65</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="I40">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="1">
         <v>46055</v>
       </c>
@@ -1130,8 +1322,12 @@
       <c r="D41">
         <v>53</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="I41">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="1">
         <v>46055</v>
       </c>
@@ -1147,8 +1343,12 @@
       <c r="E42">
         <v>31</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="I42">
+        <f t="shared" si="0"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>46055</v>
       </c>
@@ -1161,8 +1361,12 @@
       <c r="D43">
         <v>120</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="I43">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="1">
         <v>46055</v>
       </c>
@@ -1178,8 +1382,12 @@
       <c r="E44">
         <v>24</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="I44">
+        <f t="shared" si="0"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="1">
         <v>46055</v>
       </c>
@@ -1195,8 +1403,12 @@
       <c r="E45">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="I45">
+        <f t="shared" si="0"/>
+        <v>564</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="1">
         <v>46058</v>
       </c>
@@ -1209,8 +1421,12 @@
       <c r="D46">
         <v>110</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="I46">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>46058</v>
       </c>
@@ -1226,8 +1442,12 @@
       <c r="E47">
         <v>59</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="I47">
+        <f t="shared" si="0"/>
+        <v>512</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
         <v>46058</v>
       </c>
@@ -1243,8 +1463,12 @@
       <c r="E48">
         <v>11</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="I48">
+        <f t="shared" si="0"/>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="1">
         <v>46058</v>
       </c>
@@ -1257,8 +1481,12 @@
       <c r="D49">
         <v>49</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="I49">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="1">
         <v>46058</v>
       </c>
@@ -1274,8 +1502,12 @@
       <c r="E50">
         <v>11</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="I50">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="1">
         <v>46058</v>
       </c>
@@ -1291,8 +1523,12 @@
       <c r="E51">
         <v>142</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="I51">
+        <f t="shared" si="0"/>
+        <v>462</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="1">
         <v>46063</v>
       </c>
@@ -1308,8 +1544,12 @@
       <c r="E52">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="I52">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="1">
         <v>46063</v>
       </c>
@@ -1325,8 +1565,12 @@
       <c r="E53">
         <v>34</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="I53">
+        <f t="shared" si="0"/>
+        <v>625</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="1">
         <v>46063</v>
       </c>
@@ -1339,8 +1583,12 @@
       <c r="D54">
         <v>36</v>
       </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="I54">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="1">
         <v>46063</v>
       </c>
@@ -1353,8 +1601,12 @@
       <c r="D55">
         <v>28</v>
       </c>
-    </row>
-    <row r="56" spans="1:5">
+      <c r="I55">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="1">
         <v>46063</v>
       </c>
@@ -1367,8 +1619,12 @@
       <c r="D56">
         <v>306</v>
       </c>
-    </row>
-    <row r="57" spans="1:5">
+      <c r="I56">
+        <f t="shared" si="0"/>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="1">
         <v>46063</v>
       </c>
@@ -1381,8 +1637,12 @@
       <c r="D57">
         <v>331</v>
       </c>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="I57">
+        <f t="shared" si="0"/>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="1">
         <v>46063</v>
       </c>
@@ -1395,8 +1655,12 @@
       <c r="D58">
         <v>94</v>
       </c>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="I58">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="1">
         <v>46063</v>
       </c>
@@ -1412,8 +1676,12 @@
       <c r="E59">
         <v>74</v>
       </c>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="I59">
+        <f t="shared" si="0"/>
+        <v>442</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="1">
         <v>46063</v>
       </c>
@@ -1426,8 +1694,12 @@
       <c r="E60">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="I60">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>46065</v>
       </c>
@@ -1443,8 +1715,12 @@
       <c r="E61">
         <v>12</v>
       </c>
-    </row>
-    <row r="62" spans="1:5">
+      <c r="I61">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="1">
         <v>46065</v>
       </c>
@@ -1460,8 +1736,12 @@
       <c r="E62">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="I62">
+        <f t="shared" si="0"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="1">
         <v>46065</v>
       </c>
@@ -1474,8 +1754,12 @@
       <c r="D63">
         <v>111</v>
       </c>
-    </row>
-    <row r="64" spans="1:5">
+      <c r="I63">
+        <f t="shared" si="0"/>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="1">
         <v>46065</v>
       </c>
@@ -1488,8 +1772,12 @@
       <c r="D64">
         <v>190</v>
       </c>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="I64">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" s="1">
         <v>46065</v>
       </c>
@@ -1502,8 +1790,12 @@
       <c r="D65">
         <v>42</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="I65">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" s="1">
         <v>46065</v>
       </c>
@@ -1519,9 +1811,1085 @@
       <c r="E66">
         <v>82</v>
       </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="1"/>
+      <c r="I66">
+        <f t="shared" si="0"/>
+        <v>437</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67">
+        <v>153</v>
+      </c>
+      <c r="E67">
+        <v>48</v>
+      </c>
+      <c r="I67">
+        <f>D67+E67</f>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68">
+        <v>627</v>
+      </c>
+      <c r="E68">
+        <v>41</v>
+      </c>
+      <c r="I68">
+        <f>D68+E68</f>
+        <v>668</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B69" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69">
+        <v>48</v>
+      </c>
+      <c r="I69">
+        <f>D69+E69</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B70" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70">
+        <v>9</v>
+      </c>
+      <c r="I70">
+        <f>D70+E70</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B71" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71">
+        <v>139</v>
+      </c>
+      <c r="E71">
+        <v>6</v>
+      </c>
+      <c r="I71">
+        <f>D71+E71</f>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B72" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72">
+        <v>77</v>
+      </c>
+      <c r="E72">
+        <v>41</v>
+      </c>
+      <c r="I72">
+        <f>D72+E72</f>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B73" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73">
+        <v>8</v>
+      </c>
+      <c r="E73">
+        <v>9</v>
+      </c>
+      <c r="I73">
+        <f>D73+E73</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74">
+        <v>34</v>
+      </c>
+      <c r="E74">
+        <v>23</v>
+      </c>
+      <c r="I74">
+        <f>D74+E74</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75">
+        <v>163</v>
+      </c>
+      <c r="E75">
+        <v>147</v>
+      </c>
+      <c r="I75">
+        <f>D75+E75</f>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2</v>
+      </c>
+      <c r="C76" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76">
+        <v>80</v>
+      </c>
+      <c r="E76">
+        <v>5</v>
+      </c>
+      <c r="I76">
+        <f>D76+E76</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B77" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77">
+        <v>132</v>
+      </c>
+      <c r="E77">
+        <v>9</v>
+      </c>
+      <c r="I77">
+        <f>D77+E77</f>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B78" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78">
+        <v>18</v>
+      </c>
+      <c r="I78">
+        <f>D78+E78</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B79" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79">
+        <v>49</v>
+      </c>
+      <c r="I79">
+        <f>D79+E79</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B80" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80">
+        <v>81</v>
+      </c>
+      <c r="I80">
+        <f>D80+E80</f>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B81" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81">
+        <v>11</v>
+      </c>
+      <c r="I81">
+        <f>D81+E81</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82">
+        <v>46</v>
+      </c>
+      <c r="E82">
+        <v>11</v>
+      </c>
+      <c r="I82">
+        <f>D82+E82</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83">
+        <v>83</v>
+      </c>
+      <c r="I83">
+        <f>D83+E83</f>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B84" t="s">
+        <v>2</v>
+      </c>
+      <c r="C84" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84">
+        <v>155</v>
+      </c>
+      <c r="E84">
+        <v>13</v>
+      </c>
+      <c r="I84">
+        <f>D84+E84</f>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B85" t="s">
+        <v>2</v>
+      </c>
+      <c r="C85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85">
+        <v>687</v>
+      </c>
+      <c r="E85">
+        <v>193</v>
+      </c>
+      <c r="I85">
+        <f>D85+E85</f>
+        <v>880</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B86" t="s">
+        <v>2</v>
+      </c>
+      <c r="C86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86">
+        <v>32</v>
+      </c>
+      <c r="I86">
+        <f>D86+E86</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B87" t="s">
+        <v>14</v>
+      </c>
+      <c r="C87" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87">
+        <v>365</v>
+      </c>
+      <c r="I87">
+        <f>D87+E87</f>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B88" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88">
+        <v>31</v>
+      </c>
+      <c r="I88">
+        <f>D88+E88</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B89" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89">
+        <v>344</v>
+      </c>
+      <c r="E89">
+        <v>95</v>
+      </c>
+      <c r="I89">
+        <f>D89+E89</f>
+        <v>439</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B90" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90">
+        <v>316</v>
+      </c>
+      <c r="E90">
+        <v>164</v>
+      </c>
+      <c r="I90">
+        <f>D90+E90</f>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B91" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91">
+        <v>47</v>
+      </c>
+      <c r="E91">
+        <v>6</v>
+      </c>
+      <c r="I91">
+        <f>D91+E91</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B92" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92">
+        <v>144</v>
+      </c>
+      <c r="E92">
+        <v>20</v>
+      </c>
+      <c r="I92">
+        <f>D92+E92</f>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B93" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93">
+        <v>480</v>
+      </c>
+      <c r="E93">
+        <v>372</v>
+      </c>
+      <c r="I93">
+        <f>D93+E93</f>
+        <v>852</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94">
+        <v>13</v>
+      </c>
+      <c r="I94">
+        <f>D94+E94</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B95" t="s">
+        <v>2</v>
+      </c>
+      <c r="C95" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95">
+        <v>31</v>
+      </c>
+      <c r="E95">
+        <v>7</v>
+      </c>
+      <c r="I95">
+        <f>D95+E95</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B96" t="s">
+        <v>2</v>
+      </c>
+      <c r="C96" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96">
+        <v>14</v>
+      </c>
+      <c r="E96">
+        <v>110</v>
+      </c>
+      <c r="I96">
+        <f>D96+E96</f>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B97" t="s">
+        <v>14</v>
+      </c>
+      <c r="C97" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97">
+        <v>63</v>
+      </c>
+      <c r="E97">
+        <v>36</v>
+      </c>
+      <c r="I97">
+        <f>D97+E97</f>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B98" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98">
+        <v>15</v>
+      </c>
+      <c r="I98">
+        <f>D98+E98</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B99" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99">
+        <v>117</v>
+      </c>
+      <c r="I99">
+        <f>D99+E99</f>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B100" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100">
+        <v>174</v>
+      </c>
+      <c r="E100">
+        <v>19</v>
+      </c>
+      <c r="I100">
+        <f>D100+E100</f>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B101" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101">
+        <v>23</v>
+      </c>
+      <c r="I101">
+        <f>D101+E101</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102">
+        <v>31</v>
+      </c>
+      <c r="I102">
+        <f>D102+E102</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B103" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103">
+        <v>64</v>
+      </c>
+      <c r="E103">
+        <v>45</v>
+      </c>
+      <c r="I103">
+        <f t="shared" ref="I103" si="1">D103+E103</f>
+        <v>109</v>
+      </c>
+      <c r="K103" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B104" t="s">
+        <v>2</v>
+      </c>
+      <c r="C104" t="s">
+        <v>9</v>
+      </c>
+      <c r="D104">
+        <v>199</v>
+      </c>
+      <c r="E104">
+        <v>24</v>
+      </c>
+      <c r="F104">
+        <v>3</v>
+      </c>
+      <c r="H104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B105" t="s">
+        <v>2</v>
+      </c>
+      <c r="C105" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105">
+        <v>98</v>
+      </c>
+      <c r="E105">
+        <v>268</v>
+      </c>
+      <c r="F105">
+        <v>4</v>
+      </c>
+      <c r="H105">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B106" t="s">
+        <v>14</v>
+      </c>
+      <c r="C106" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106">
+        <v>160</v>
+      </c>
+      <c r="E106">
+        <v>125</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B107" t="s">
+        <v>14</v>
+      </c>
+      <c r="C107" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107">
+        <v>102</v>
+      </c>
+      <c r="E107">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B108" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" t="s">
+        <v>9</v>
+      </c>
+      <c r="D108">
+        <v>190</v>
+      </c>
+      <c r="F108">
+        <v>18</v>
+      </c>
+      <c r="H108">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B109" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109">
+        <v>583</v>
+      </c>
+      <c r="E109">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B110" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110">
+        <v>23</v>
+      </c>
+      <c r="E110">
+        <v>6</v>
+      </c>
+      <c r="F110">
+        <v>2</v>
+      </c>
+      <c r="H110">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B111" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111">
+        <v>47</v>
+      </c>
+      <c r="E111">
+        <v>17</v>
+      </c>
+      <c r="F111">
+        <v>6</v>
+      </c>
+      <c r="H111">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B112" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112">
+        <v>377</v>
+      </c>
+      <c r="E112">
+        <v>388</v>
+      </c>
+      <c r="F112">
+        <v>11</v>
+      </c>
+      <c r="H112">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B113" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B114" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114">
+        <v>290</v>
+      </c>
+      <c r="E114">
+        <v>54</v>
+      </c>
+      <c r="H114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B115" t="s">
+        <v>14</v>
+      </c>
+      <c r="C115" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115">
+        <v>91</v>
+      </c>
+      <c r="E115">
+        <v>93</v>
+      </c>
+      <c r="H115">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B116" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" t="s">
+        <v>10</v>
+      </c>
+      <c r="D116">
+        <v>60</v>
+      </c>
+      <c r="E116">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B117" t="s">
+        <v>5</v>
+      </c>
+      <c r="C117" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117">
+        <v>31</v>
+      </c>
+      <c r="E117">
+        <v>27</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B118" t="s">
+        <v>5</v>
+      </c>
+      <c r="C118" t="s">
+        <v>10</v>
+      </c>
+      <c r="D118">
+        <v>138</v>
+      </c>
+      <c r="E118">
+        <v>22</v>
+      </c>
+      <c r="H118">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B119" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" t="s">
+        <v>9</v>
+      </c>
+      <c r="D119">
+        <v>9</v>
+      </c>
+      <c r="E119">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B120" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120">
+        <v>295</v>
+      </c>
+      <c r="E120">
+        <v>181</v>
+      </c>
+      <c r="H120">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
